--- a/public/formsExcelTemplates/Emergencia.xlsx
+++ b/public/formsExcelTemplates/Emergencia.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>Sección</t>
   </si>
@@ -33,12 +33,21 @@
     <t>Institución</t>
   </si>
   <si>
+    <t xml:space="preserve">Clínica Hospital</t>
+  </si>
+  <si>
     <t xml:space="preserve">Código único</t>
   </si>
   <si>
+    <t xml:space="preserve"> -</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nombre del establecimiento</t>
   </si>
   <si>
+    <t xml:space="preserve">San José</t>
+  </si>
+  <si>
     <t xml:space="preserve">Datos del paciente</t>
   </si>
   <si>
@@ -49,6 +58,12 @@
   </si>
   <si>
     <t xml:space="preserve">Fecha y hora de ingreso</t>
+  </si>
+  <si>
+    <t>Cédula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipo de sangre</t>
   </si>
   <si>
     <t xml:space="preserve">Constantes vitales</t>
@@ -139,7 +154,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="22">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -157,22 +172,107 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="medium">
-        <color auto="1"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color theme="1"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
@@ -184,22 +284,20 @@
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
+      <top style="none"/>
+      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color auto="1"/>
       </left>
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color auto="1"/>
       </top>
       <bottom style="thin">
@@ -211,10 +309,10 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
         <color auto="1"/>
       </top>
       <bottom style="thin">
@@ -223,43 +321,69 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
         <color auto="1"/>
       </right>
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color auto="1"/>
       </left>
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
         <color auto="1"/>
       </top>
       <bottom style="thin">
@@ -274,7 +398,7 @@
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color auto="1"/>
       </top>
       <bottom style="thin">
@@ -286,91 +410,38 @@
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="25">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -384,23 +455,30 @@
     <xf fontId="0" fillId="0" borderId="4" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="4" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="4" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="4" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -408,13 +486,31 @@
     <xf fontId="0" fillId="0" borderId="12" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="13" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="15" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="16" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="17" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="18" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="19" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="2" fillId="0" borderId="20" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="2" fillId="0" borderId="21" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -969,160 +1065,180 @@
       <c r="B2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="6"/>
+      <c r="C2" s="6" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="9"/>
+      <c r="A3" s="4"/>
+      <c r="B3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="4" ht="15">
-      <c r="A4" s="10"/>
-      <c r="B4" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="12"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>7</v>
+      <c r="A5" s="8" t="s">
+        <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="6"/>
+        <v>11</v>
+      </c>
+      <c r="C5" s="5"/>
     </row>
     <row r="6">
-      <c r="A6" s="7"/>
-      <c r="B6" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="9"/>
+      <c r="A6" s="9"/>
+      <c r="B6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="5"/>
     </row>
     <row r="7" ht="15">
-      <c r="A7" s="10"/>
-      <c r="B7" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="12"/>
+      <c r="A7" s="9"/>
+      <c r="B7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="5"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="6"/>
+      <c r="A8" s="9"/>
+      <c r="B8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="7"/>
     </row>
     <row r="9">
-      <c r="A9" s="7"/>
-      <c r="B9" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="9"/>
+      <c r="A9" s="10"/>
+      <c r="B9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="7"/>
     </row>
     <row r="10">
-      <c r="A10" s="7"/>
-      <c r="B10" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="9"/>
+      <c r="A10" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="13"/>
     </row>
     <row r="11">
-      <c r="A11" s="7"/>
-      <c r="B11" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="9"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="15"/>
     </row>
     <row r="12">
-      <c r="A12" s="7"/>
-      <c r="B12" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="9"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="15"/>
     </row>
     <row r="13" ht="15">
-      <c r="A13" s="10"/>
-      <c r="B13" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="12"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="15"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="6"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="15"/>
     </row>
     <row r="15" ht="15">
-      <c r="A15" s="10"/>
-      <c r="B15" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="12"/>
+      <c r="A15" s="16"/>
+      <c r="B15" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="18"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="6"/>
+      <c r="A16" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="21"/>
     </row>
     <row r="17" ht="15">
-      <c r="A17" s="10"/>
-      <c r="B17" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="12"/>
+      <c r="A17" s="16"/>
+      <c r="B17" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="18"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="6"/>
+      <c r="A18" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="21"/>
     </row>
     <row r="19">
-      <c r="A19" s="7"/>
-      <c r="B19" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" s="9"/>
+      <c r="A19" s="16"/>
+      <c r="B19" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="18"/>
     </row>
     <row r="20" ht="15">
-      <c r="A20" s="10"/>
-      <c r="B20" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" s="12"/>
+      <c r="A20" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="21"/>
     </row>
     <row r="21" ht="15">
-      <c r="A21" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="14"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="14" t="s">
+        <v>31</v>
+      </c>
       <c r="C21" s="15"/>
+    </row>
+    <row r="22" ht="15">
+      <c r="A22" s="16"/>
+      <c r="B22" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="18"/>
+    </row>
+    <row r="23" ht="14.25">
+      <c r="A23" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="23"/>
+      <c r="C23" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A2:A4"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="A8:A13"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A5:A9"/>
+    <mergeCell ref="A10:A15"/>
     <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A23:C23"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
